--- a/tasks/finalpool/fetch-howtocook-wellness-notion-email/groundtruth_workspace/Wellness_Report.xlsx
+++ b/tasks/finalpool/fetch-howtocook-wellness-notion-email/groundtruth_workspace/Wellness_Report.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,20 +440,10 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Calories</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Calories</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Protein_g</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Meets_Guidelines</t>
         </is>
@@ -465,18 +455,10 @@
           <t>Kung Pao Chicken</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Main Dish</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" t="n">
         <v>450</v>
       </c>
-      <c r="D2" t="n">
-        <v>35</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -488,18 +470,10 @@
           <t>Tomato Egg Stir Fry</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Quick Meal</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
+      <c r="B3" t="n">
         <v>280</v>
       </c>
-      <c r="D3" t="n">
-        <v>18</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -511,18 +485,10 @@
           <t>Steamed Fish</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Seafood</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4" t="n">
         <v>220</v>
       </c>
-      <c r="D4" t="n">
-        <v>32</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -534,18 +500,10 @@
           <t>Fried Rice</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Staple</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+      <c r="B5" t="n">
         <v>520</v>
       </c>
-      <c r="D5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -557,18 +515,10 @@
           <t>Hot and Sour Soup</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Soup</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+      <c r="B6" t="n">
         <v>180</v>
       </c>
-      <c r="D6" t="n">
-        <v>12</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
